--- a/files/港岛-半山区西部-Upper Central.xlsx
+++ b/files/港岛-半山区西部-Upper Central.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upper Central 销控表" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -20,7 +19,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="14">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -42,65 +41,8 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="007F7F7F"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="007F7F7F"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00004D00"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00002060"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00002060"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <color rgb="00660000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00660000"/>
-      <sz val="11"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="9"/>
-    </font>
-    <font>
-      <name val="Microsoft YaHei"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="11"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="3">
     <fill>
       <patternFill/>
     </fill>
@@ -111,42 +53,6 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
-        <bgColor rgb="00FFFFFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9F5A9"/>
-        <bgColor rgb="00A9F5A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00A9D0F5"/>
-        <bgColor rgb="00A9D0F5"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F5A9A9"/>
-        <bgColor rgb="00F5A9A9"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC000"/>
-        <bgColor rgb="00FFC000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E5E5E5"/>
-        <bgColor rgb="00E5E5E5"/>
       </patternFill>
     </fill>
   </fills>
@@ -176,7 +82,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -192,48 +98,6 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1073,7 +937,7 @@
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-31</t>
         </is>
       </c>
       <c r="H11" s="5" t="n">
@@ -1211,7 +1075,7 @@
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-10</t>
         </is>
       </c>
       <c r="H14" s="5" t="n">
@@ -1257,7 +1121,7 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-14</t>
         </is>
       </c>
       <c r="H15" s="5" t="n">
@@ -1349,7 +1213,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="H17" s="5" t="n">
@@ -1395,7 +1259,7 @@
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-24</t>
         </is>
       </c>
       <c r="H18" s="5" t="n">
@@ -1533,7 +1397,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="H21" s="5" t="n">
@@ -1579,7 +1443,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-14</t>
         </is>
       </c>
       <c r="H22" s="5" t="n">
@@ -1625,7 +1489,7 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-06-16</t>
         </is>
       </c>
       <c r="H23" s="5" t="n">
@@ -1717,7 +1581,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="H25" s="5" t="n">
@@ -1763,7 +1627,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-27</t>
         </is>
       </c>
       <c r="H26" s="5" t="n">
@@ -1809,7 +1673,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-27</t>
         </is>
       </c>
       <c r="H27" s="5" t="n">
@@ -1855,7 +1719,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H28" s="5" t="n">
@@ -1947,7 +1811,7 @@
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-03</t>
         </is>
       </c>
       <c r="H30" s="5" t="n">
@@ -1993,7 +1857,7 @@
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-11</t>
         </is>
       </c>
       <c r="H31" s="5" t="n">
@@ -2039,7 +1903,7 @@
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-01-13</t>
         </is>
       </c>
       <c r="H32" s="5" t="n">
@@ -2085,7 +1949,7 @@
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-08</t>
         </is>
       </c>
       <c r="H33" s="5" t="n">
@@ -2131,7 +1995,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H34" s="5" t="n">
@@ -2177,7 +2041,7 @@
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-19</t>
         </is>
       </c>
       <c r="H35" s="5" t="n">
@@ -2223,7 +2087,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-07</t>
         </is>
       </c>
       <c r="H36" s="5" t="n">
@@ -2269,7 +2133,7 @@
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="H37" s="5" t="n">
@@ -2315,7 +2179,7 @@
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-02-20</t>
         </is>
       </c>
       <c r="H38" s="5" t="n">
@@ -2361,7 +2225,7 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="H39" s="5" t="n">
@@ -2407,7 +2271,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-26</t>
         </is>
       </c>
       <c r="H40" s="5" t="n">
@@ -2453,7 +2317,7 @@
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H41" s="5" t="n">
@@ -2499,7 +2363,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-17</t>
         </is>
       </c>
       <c r="H42" s="5" t="n">
@@ -2545,7 +2409,7 @@
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="H43" s="5" t="n">
@@ -2591,7 +2455,7 @@
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-12</t>
         </is>
       </c>
       <c r="H44" s="5" t="n">
@@ -2637,7 +2501,7 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-28</t>
         </is>
       </c>
       <c r="H45" s="5" t="n">
@@ -2683,7 +2547,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-04</t>
         </is>
       </c>
       <c r="H46" s="5" t="n">
@@ -2729,7 +2593,7 @@
       </c>
       <c r="G47" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-20</t>
         </is>
       </c>
       <c r="H47" s="5" t="n">
@@ -2775,7 +2639,7 @@
       </c>
       <c r="G48" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H48" s="5" t="n">
@@ -2821,7 +2685,7 @@
       </c>
       <c r="G49" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-23</t>
         </is>
       </c>
       <c r="H49" s="5" t="n">
@@ -2867,7 +2731,7 @@
       </c>
       <c r="G50" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H50" s="5" t="n">
@@ -2913,7 +2777,7 @@
       </c>
       <c r="G51" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-05</t>
         </is>
       </c>
       <c r="H51" s="5" t="n">
@@ -2959,7 +2823,7 @@
       </c>
       <c r="G52" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="H52" s="5" t="n">
@@ -3005,7 +2869,7 @@
       </c>
       <c r="G53" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-26</t>
         </is>
       </c>
       <c r="H53" s="5" t="n">
@@ -3051,7 +2915,7 @@
       </c>
       <c r="G54" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-27</t>
         </is>
       </c>
       <c r="H54" s="5" t="n">
@@ -3097,7 +2961,7 @@
       </c>
       <c r="G55" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-05-26</t>
         </is>
       </c>
       <c r="H55" s="5" t="n">
@@ -3143,7 +3007,7 @@
       </c>
       <c r="G56" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-01-06</t>
         </is>
       </c>
       <c r="H56" s="5" t="n">
@@ -3189,7 +3053,7 @@
       </c>
       <c r="G57" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="H57" s="5" t="n">
@@ -3235,7 +3099,7 @@
       </c>
       <c r="G58" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="H58" s="5" t="n">
@@ -3281,7 +3145,7 @@
       </c>
       <c r="G59" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-30</t>
         </is>
       </c>
       <c r="H59" s="5" t="n">
@@ -3327,7 +3191,7 @@
       </c>
       <c r="G60" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-26</t>
         </is>
       </c>
       <c r="H60" s="5" t="n">
@@ -3373,7 +3237,7 @@
       </c>
       <c r="G61" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="H61" s="5" t="n">
@@ -3419,7 +3283,7 @@
       </c>
       <c r="G62" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-10-15</t>
         </is>
       </c>
       <c r="H62" s="5" t="n">
@@ -3465,7 +3329,7 @@
       </c>
       <c r="G63" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-10</t>
         </is>
       </c>
       <c r="H63" s="5" t="n">
@@ -3511,7 +3375,7 @@
       </c>
       <c r="G64" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="H64" s="5" t="n">
@@ -3557,7 +3421,7 @@
       </c>
       <c r="G65" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-19</t>
         </is>
       </c>
       <c r="H65" s="5" t="n">
@@ -3603,7 +3467,7 @@
       </c>
       <c r="G66" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H66" s="5" t="n">
@@ -3649,7 +3513,7 @@
       </c>
       <c r="G67" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-04-16</t>
         </is>
       </c>
       <c r="H67" s="5" t="n">
@@ -3695,7 +3559,7 @@
       </c>
       <c r="G68" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-06-12</t>
         </is>
       </c>
       <c r="H68" s="5" t="n">
@@ -3741,7 +3605,7 @@
       </c>
       <c r="G69" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H69" s="5" t="n">
@@ -3787,7 +3651,7 @@
       </c>
       <c r="G70" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="H70" s="5" t="n">
@@ -3833,7 +3697,7 @@
       </c>
       <c r="G71" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-21</t>
         </is>
       </c>
       <c r="H71" s="5" t="n">
@@ -3879,7 +3743,7 @@
       </c>
       <c r="G72" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-08</t>
         </is>
       </c>
       <c r="H72" s="5" t="n">
@@ -3925,7 +3789,7 @@
       </c>
       <c r="G73" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="H73" s="5" t="n">
@@ -3971,7 +3835,7 @@
       </c>
       <c r="G74" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-19</t>
         </is>
       </c>
       <c r="H74" s="5" t="n">
@@ -4017,7 +3881,7 @@
       </c>
       <c r="G75" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-12-17</t>
         </is>
       </c>
       <c r="H75" s="5" t="n">
@@ -4063,7 +3927,7 @@
       </c>
       <c r="G76" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-09</t>
         </is>
       </c>
       <c r="H76" s="5" t="n">
@@ -4109,7 +3973,7 @@
       </c>
       <c r="G77" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-23</t>
         </is>
       </c>
       <c r="H77" s="5" t="n">
@@ -4155,7 +4019,7 @@
       </c>
       <c r="G78" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H78" s="5" t="n">
@@ -4201,7 +4065,7 @@
       </c>
       <c r="G79" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-08-20</t>
         </is>
       </c>
       <c r="H79" s="5" t="n">
@@ -4247,7 +4111,7 @@
       </c>
       <c r="G80" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-07-13</t>
         </is>
       </c>
       <c r="H80" s="5" t="n">
@@ -4293,7 +4157,7 @@
       </c>
       <c r="G81" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-24</t>
         </is>
       </c>
       <c r="H81" s="5" t="n">
@@ -4339,7 +4203,7 @@
       </c>
       <c r="G82" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-01</t>
         </is>
       </c>
       <c r="H82" s="5" t="n">
@@ -4385,7 +4249,7 @@
       </c>
       <c r="G83" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-29</t>
         </is>
       </c>
       <c r="H83" s="5" t="n">
@@ -4431,7 +4295,7 @@
       </c>
       <c r="G84" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2024-11-18</t>
         </is>
       </c>
       <c r="H84" s="5" t="n">
@@ -4477,7 +4341,7 @@
       </c>
       <c r="G85" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-12-18</t>
         </is>
       </c>
       <c r="H85" s="5" t="n">
@@ -4523,7 +4387,7 @@
       </c>
       <c r="G86" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2026-02-05</t>
         </is>
       </c>
       <c r="H86" s="5" t="n">
@@ -4569,7 +4433,7 @@
       </c>
       <c r="G87" s="3" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>2025-03-30</t>
         </is>
       </c>
       <c r="H87" s="5" t="n">
@@ -4591,992 +4455,4 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:F27"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="12" customWidth="1" min="1" max="1"/>
-    <col width="18" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="40" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Upper Central - Upper Central 销控网格图</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="20" customHeight="1">
-      <c r="A2" s="6" t="inlineStr">
-        <is>
-          <t>总套数</t>
-        </is>
-      </c>
-      <c r="B2" s="7" t="inlineStr">
-        <is>
-          <t>在售 (Sale)</t>
-        </is>
-      </c>
-      <c r="C2" s="8" t="inlineStr">
-        <is>
-          <t>已定价未售</t>
-        </is>
-      </c>
-      <c r="D2" s="9" t="inlineStr">
-        <is>
-          <t>已售 (Sold)</t>
-        </is>
-      </c>
-      <c r="E2" s="10" t="inlineStr">
-        <is>
-          <t>暂停销售</t>
-        </is>
-      </c>
-      <c r="F2" s="6" t="inlineStr">
-        <is>
-          <t>待售 (Pending)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="25" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
-        <is>
-          <t>85 套</t>
-        </is>
-      </c>
-      <c r="B3" s="12" t="inlineStr">
-        <is>
-          <t>4 套</t>
-        </is>
-      </c>
-      <c r="C3" s="13" t="inlineStr">
-        <is>
-          <t>8 套</t>
-        </is>
-      </c>
-      <c r="D3" s="14" t="inlineStr">
-        <is>
-          <t>73 套</t>
-        </is>
-      </c>
-      <c r="E3" s="15" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-      <c r="F3" s="11" t="inlineStr">
-        <is>
-          <t>0 套</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="25" customHeight="1">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>楼层\房号</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>A</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>B</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>C</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>D</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>E</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="65" customHeight="1">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>30/F</t>
-        </is>
-      </c>
-      <c r="B6" s="16" t="inlineStr">
-        <is>
-          <t>A | 177呎 (开放式)
-$601万
-$33,944/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C6" s="16" t="inlineStr">
-        <is>
-          <t>B | 156呎 (开放式)
-$519万
-$33,288/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D6" s="16" t="inlineStr">
-        <is>
-          <t>C | 242呎 (开放式)
-$849万
-$35,066/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E6" s="16" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$856万
-$35,082/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F6" s="17" t="inlineStr"/>
-    </row>
-    <row r="7" ht="65" customHeight="1">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>29/F</t>
-        </is>
-      </c>
-      <c r="B7" s="16" t="inlineStr">
-        <is>
-          <t>A | 193呎 (开放式)
-$787万
-$40,798/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="C7" s="16" t="inlineStr">
-        <is>
-          <t>B | 167呎 (开放式)
-$665万
-$39,808/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="D7" s="16" t="inlineStr">
-        <is>
-          <t>C | 240呎 (开放式)
-$969万
-$40,379/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="E7" s="16" t="inlineStr">
-        <is>
-          <t>D | 242呎 (开放式)
-$978万
-$40,397/呎
-(已定价未售)</t>
-        </is>
-      </c>
-      <c r="F7" s="17" t="inlineStr"/>
-    </row>
-    <row r="8" ht="65" customHeight="1">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>28/F</t>
-        </is>
-      </c>
-      <c r="B8" s="18" t="inlineStr">
-        <is>
-          <t>A | 197呎 (开放式)
-$728万
-$36,959/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr"/>
-      <c r="D8" s="17" t="inlineStr"/>
-      <c r="E8" s="18" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$911万
-$37,352/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F8" s="19" t="inlineStr">
-        <is>
-          <t>E | 389呎 (2房)
-$1,257万
-$32,303/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="65" customHeight="1">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>27/F</t>
-        </is>
-      </c>
-      <c r="B9" s="18" t="inlineStr">
-        <is>
-          <t>A | 195呎 (开放式)
-$718万
-$36,831/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr"/>
-      <c r="D9" s="17" t="inlineStr"/>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$698万
-$28,623/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F9" s="19" t="inlineStr">
-        <is>
-          <t>E | 389呎 (2房)
-$1,181万
-$30,357/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="65" customHeight="1">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>26/F</t>
-        </is>
-      </c>
-      <c r="B10" s="19" t="inlineStr">
-        <is>
-          <t>A | 197呎 (开放式)
-$626万
-$31,797/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr"/>
-      <c r="D10" s="17" t="inlineStr"/>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$692万
-$28,365/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F10" s="19" t="inlineStr">
-        <is>
-          <t>E | 389呎 (2房)
-$1,170万
-$30,087/呎
-(已售)</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="65" customHeight="1">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>25/F</t>
-        </is>
-      </c>
-      <c r="B11" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$589万
-$30,036/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$470万
-$28,000/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D11" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$678万
-$28,112/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E11" s="18" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$843万
-$34,553/呎
-(在售)</t>
-        </is>
-      </c>
-      <c r="F11" s="17" t="inlineStr"/>
-    </row>
-    <row r="12" ht="65" customHeight="1">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>23/F</t>
-        </is>
-      </c>
-      <c r="B12" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$563万
-$28,714/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$436万
-$25,946/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D12" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$661万
-$27,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E12" s="19" t="inlineStr">
-        <is>
-          <t>D | 242呎 (开放式)
-$689万
-$28,471/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="F12" s="17" t="inlineStr"/>
-    </row>
-    <row r="13" ht="65" customHeight="1">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>22/F</t>
-        </is>
-      </c>
-      <c r="B13" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$515万
-$26,296/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C13" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$432万
-$25,690/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D13" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$674万
-$27,963/呎
-(26年-06月)</t>
-        </is>
-      </c>
-      <c r="E13" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$662万
-$27,148/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F13" s="17" t="inlineStr"/>
-    </row>
-    <row r="14" ht="65" customHeight="1">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>21/F</t>
-        </is>
-      </c>
-      <c r="B14" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$536万
-$27,347/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C14" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$462万
-$27,518/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D14" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$617万
-$25,606/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E14" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$625万
-$25,611/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F14" s="17" t="inlineStr"/>
-    </row>
-    <row r="15" ht="65" customHeight="1">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>20/F</t>
-        </is>
-      </c>
-      <c r="B15" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$516万
-$26,316/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C15" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$423万
-$25,190/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D15" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$611万
-$25,365/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E15" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$644万
-$26,381/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F15" s="17" t="inlineStr"/>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>19/F</t>
-        </is>
-      </c>
-      <c r="B16" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$501万
-$25,556/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$440万
-$26,196/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D16" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$605万
-$25,120/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E16" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$638万
-$26,127/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F16" s="17" t="inlineStr"/>
-    </row>
-    <row r="17" ht="65" customHeight="1">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>18/F</t>
-        </is>
-      </c>
-      <c r="B17" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$508万
-$25,944/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$417万
-$24,821/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D17" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$627万
-$26,004/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E17" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$635万
-$26,012/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F17" s="17" t="inlineStr"/>
-    </row>
-    <row r="18" ht="65" customHeight="1">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>17/F</t>
-        </is>
-      </c>
-      <c r="B18" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$501万
-$25,566/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C18" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$444万
-$26,440/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D18" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$618万
-$25,631/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E18" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$601万
-$24,648/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F18" s="17" t="inlineStr"/>
-    </row>
-    <row r="19" ht="65" customHeight="1">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>16/F</t>
-        </is>
-      </c>
-      <c r="B19" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$487万
-$24,827/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C19" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$407万
-$24,214/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D19" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$588万
-$24,407/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E19" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$596万
-$24,410/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F19" s="17" t="inlineStr"/>
-    </row>
-    <row r="20" ht="65" customHeight="1">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>15/F</t>
-        </is>
-      </c>
-      <c r="B20" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$492万
-$25,077/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C20" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$436万
-$25,923/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D20" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$606万
-$25,145/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E20" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$590万
-$24,176/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F20" s="17" t="inlineStr"/>
-    </row>
-    <row r="21" ht="65" customHeight="1">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>12/F</t>
-        </is>
-      </c>
-      <c r="B21" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$506万
-$25,842/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$399万
-$23,738/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D21" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$600万
-$24,905/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E21" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$596万
-$24,422/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F21" s="17" t="inlineStr"/>
-    </row>
-    <row r="22" ht="65" customHeight="1">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>11/F</t>
-        </is>
-      </c>
-      <c r="B22" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$501万
-$25,566/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C22" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$427万
-$25,411/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D22" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$594万
-$24,660/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E22" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$602万
-$24,660/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F22" s="17" t="inlineStr"/>
-    </row>
-    <row r="23" ht="65" customHeight="1">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>10/F</t>
-        </is>
-      </c>
-      <c r="B23" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$478万
-$24,362/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C23" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$410万
-$24,429/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D23" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$566万
-$23,481/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E23" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$573万
-$23,484/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F23" s="17" t="inlineStr"/>
-    </row>
-    <row r="24" ht="65" customHeight="1">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>9/F</t>
-        </is>
-      </c>
-      <c r="B24" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$464万
-$23,653/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C24" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$419万
-$24,917/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D24" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$560万
-$23,257/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E24" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$579万
-$23,725/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F24" s="17" t="inlineStr"/>
-    </row>
-    <row r="25" ht="65" customHeight="1">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>8/F</t>
-        </is>
-      </c>
-      <c r="B25" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$461万
-$23,541/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C25" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$404万
-$24,071/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D25" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$580万
-$24,079/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E25" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$565万
-$23,148/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F25" s="17" t="inlineStr"/>
-    </row>
-    <row r="26" ht="65" customHeight="1">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>7/F</t>
-        </is>
-      </c>
-      <c r="B26" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$473万
-$24,128/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C26" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$410万
-$24,429/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D26" s="19" t="inlineStr">
-        <is>
-          <t>C | 241呎 (开放式)
-$572万
-$23,734/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E26" s="19" t="inlineStr">
-        <is>
-          <t>D | 244呎 (开放式)
-$557万
-$22,816/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F26" s="17" t="inlineStr"/>
-    </row>
-    <row r="27" ht="65" customHeight="1">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>6/F</t>
-        </is>
-      </c>
-      <c r="B27" s="19" t="inlineStr">
-        <is>
-          <t>A | 196呎 (开放式)
-$450万
-$22,980/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="C27" s="19" t="inlineStr">
-        <is>
-          <t>B | 168呎 (开放式)
-$406万
-$24,185/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="D27" s="19" t="inlineStr">
-        <is>
-          <t>C | 205呎 (开放式)
-$540万
-$26,322/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="E27" s="19" t="inlineStr">
-        <is>
-          <t>D | 209呎 (开放式)
-$548万
-$26,196/呎
-(已售)</t>
-        </is>
-      </c>
-      <c r="F27" s="17" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A1:F1"/>
-  </mergeCells>
-  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
-  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
 </file>
--- a/files/港岛-半山区西部-Upper Central.xlsx
+++ b/files/港岛-半山区西部-Upper Central.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="销控汇总明细" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Upper Central" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19,7 +20,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="$#,##0"/>
   </numFmts>
-  <fonts count="4">
+  <fonts count="20">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -41,8 +42,96 @@
       <name val="Microsoft YaHei"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00002060"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00660000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="007F7F7F"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="007F7F7F"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00002060"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <b val="1"/>
+      <color rgb="00004D00"/>
+      <sz val="8"/>
+    </font>
+    <font>
+      <name val="Microsoft YaHei"/>
+      <color rgb="00660000"/>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="9">
     <fill>
       <patternFill/>
     </fill>
@@ -53,6 +142,42 @@
       <patternFill patternType="solid">
         <fgColor rgb="00F2F2F2"/>
         <bgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFFFFF"/>
+        <bgColor rgb="00FFFFFF"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9F5A9"/>
+        <bgColor rgb="00A9F5A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00A9D0F5"/>
+        <bgColor rgb="00A9D0F5"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00F5A9A9"/>
+        <bgColor rgb="00F5A9A9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC000"/>
+        <bgColor rgb="00FFC000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8E8E8"/>
+        <bgColor rgb="00E8E8E8"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +207,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="24">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -98,6 +223,60 @@
     </xf>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -474,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="13" customWidth="1" min="8" max="8"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>
@@ -4455,4 +4634,992 @@
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:F26"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="8" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="6" t="inlineStr">
+        <is>
+          <t>Upper Central 销控网格图</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="20" customHeight="1">
+      <c r="A2" s="7" t="inlineStr">
+        <is>
+          <t>总套数</t>
+        </is>
+      </c>
+      <c r="B2" s="8" t="inlineStr">
+        <is>
+          <t>在售 (Sale)</t>
+        </is>
+      </c>
+      <c r="C2" s="9" t="inlineStr">
+        <is>
+          <t>已定价未售</t>
+        </is>
+      </c>
+      <c r="D2" s="10" t="inlineStr">
+        <is>
+          <t>已售 (Sold)</t>
+        </is>
+      </c>
+      <c r="E2" s="11" t="inlineStr">
+        <is>
+          <t>暂停销售</t>
+        </is>
+      </c>
+      <c r="F2" s="12" t="inlineStr">
+        <is>
+          <t>待售 (Pending)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="20" customHeight="1">
+      <c r="A3" s="13" t="inlineStr">
+        <is>
+          <t>85</t>
+        </is>
+      </c>
+      <c r="B3" s="14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C3" s="15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D3" s="16" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="E3" s="17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F3" s="18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="18" customHeight="1">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>楼层</t>
+        </is>
+      </c>
+      <c r="B4" s="19" t="inlineStr">
+        <is>
+          <t>A</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr">
+        <is>
+          <t>B</t>
+        </is>
+      </c>
+      <c r="D4" s="19" t="inlineStr">
+        <is>
+          <t>C</t>
+        </is>
+      </c>
+      <c r="E4" s="19" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="F4" s="19" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="58" customHeight="1">
+      <c r="A5" s="19" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="B5" s="20" t="inlineStr">
+        <is>
+          <t>A | 177呎 (开放式)
+$601万
+$33,944/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C5" s="20" t="inlineStr">
+        <is>
+          <t>B | 156呎 (开放式)
+$519万
+$33,288/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D5" s="20" t="inlineStr">
+        <is>
+          <t>C | 242呎 (开放式)
+$849万
+$35,066/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$856万
+$35,082/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F5" s="21" t="inlineStr"/>
+    </row>
+    <row r="6" ht="58" customHeight="1">
+      <c r="A6" s="19" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>A | 193呎 (开放式)
+$787万
+$40,798/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>B | 167呎 (开放式)
+$665万
+$39,808/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>C | 240呎 (开放式)
+$969万
+$40,379/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="inlineStr">
+        <is>
+          <t>D | 242呎 (开放式)
+$978万
+$40,397/呎
+(已定价未售)</t>
+        </is>
+      </c>
+      <c r="F6" s="21" t="inlineStr"/>
+    </row>
+    <row r="7" ht="58" customHeight="1">
+      <c r="A7" s="19" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>A | 197呎 (开放式)
+$728万
+$36,959/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C7" s="21" t="inlineStr"/>
+      <c r="D7" s="21" t="inlineStr"/>
+      <c r="E7" s="22" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$911万
+$37,352/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F7" s="23" t="inlineStr">
+        <is>
+          <t>E | 389呎 (2房)
+$1257万
+$32,303/呎
+(26年-03月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="58" customHeight="1">
+      <c r="A8" s="19" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>A | 195呎 (开放式)
+$718万
+$36,831/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="C8" s="21" t="inlineStr"/>
+      <c r="D8" s="21" t="inlineStr"/>
+      <c r="E8" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$698万
+$28,623/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F8" s="23" t="inlineStr">
+        <is>
+          <t>E | 389呎 (2房)
+$1181万
+$30,357/呎
+(25年-12月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="58" customHeight="1">
+      <c r="A9" s="19" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>A | 197呎 (开放式)
+$626万
+$31,797/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C9" s="21" t="inlineStr"/>
+      <c r="D9" s="21" t="inlineStr"/>
+      <c r="E9" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$692万
+$28,365/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F9" s="23" t="inlineStr">
+        <is>
+          <t>E | 389呎 (2房)
+$1170万
+$30,087/呎
+(26年-02月)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="58" customHeight="1">
+      <c r="A10" s="19" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="B10" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$589万
+$30,036/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="C10" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$470万
+$28,000/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="D10" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$678万
+$28,112/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E10" s="22" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$843万
+$34,553/呎
+(在售)</t>
+        </is>
+      </c>
+      <c r="F10" s="21" t="inlineStr"/>
+    </row>
+    <row r="11" ht="58" customHeight="1">
+      <c r="A11" s="19" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="B11" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$563万
+$28,714/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C11" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$436万
+$25,946/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D11" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$661万
+$27,411/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E11" s="23" t="inlineStr">
+        <is>
+          <t>D | 242呎 (开放式)
+$689万
+$28,471/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="F11" s="21" t="inlineStr"/>
+    </row>
+    <row r="12" ht="58" customHeight="1">
+      <c r="A12" s="19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$515万
+$26,296/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C12" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$432万
+$25,690/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="D12" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$674万
+$27,963/呎
+(26年-06月)</t>
+        </is>
+      </c>
+      <c r="E12" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$662万
+$27,148/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F12" s="21" t="inlineStr"/>
+    </row>
+    <row r="13" ht="58" customHeight="1">
+      <c r="A13" s="19" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="B13" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$536万
+$27,347/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="C13" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$462万
+$27,518/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D13" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$617万
+$25,606/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E13" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$625万
+$25,611/呎
+(25年-01月)</t>
+        </is>
+      </c>
+      <c r="F13" s="21" t="inlineStr"/>
+    </row>
+    <row r="14" ht="58" customHeight="1">
+      <c r="A14" s="19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="B14" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$516万
+$26,316/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C14" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$423万
+$25,190/呎
+(25年-02月)</t>
+        </is>
+      </c>
+      <c r="D14" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$611万
+$25,365/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E14" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$644万
+$26,381/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F14" s="21" t="inlineStr"/>
+    </row>
+    <row r="15" ht="58" customHeight="1">
+      <c r="A15" s="19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="B15" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$501万
+$25,556/呎
+(25年-11月)</t>
+        </is>
+      </c>
+      <c r="C15" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$440万
+$26,196/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D15" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$605万
+$25,120/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E15" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$638万
+$26,127/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="F15" s="21" t="inlineStr"/>
+    </row>
+    <row r="16" ht="58" customHeight="1">
+      <c r="A16" s="19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B16" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$508万
+$25,944/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C16" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$417万
+$24,821/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="D16" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$627万
+$26,004/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="E16" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$635万
+$26,012/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F16" s="21" t="inlineStr"/>
+    </row>
+    <row r="17" ht="58" customHeight="1">
+      <c r="A17" s="19" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B17" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$501万
+$25,566/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="C17" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$444万
+$26,440/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D17" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$618万
+$25,631/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E17" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$601万
+$24,648/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F17" s="21" t="inlineStr"/>
+    </row>
+    <row r="18" ht="58" customHeight="1">
+      <c r="A18" s="19" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B18" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$487万
+$24,827/呎
+(25年-05月)</t>
+        </is>
+      </c>
+      <c r="C18" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$407万
+$24,214/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D18" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$588万
+$24,407/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="E18" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$596万
+$24,410/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="F18" s="21" t="inlineStr"/>
+    </row>
+    <row r="19" ht="58" customHeight="1">
+      <c r="A19" s="19" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B19" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$492万
+$25,077/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C19" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$436万
+$25,923/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D19" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$606万
+$25,145/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E19" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$590万
+$24,176/呎
+(26年-01月)</t>
+        </is>
+      </c>
+      <c r="F19" s="21" t="inlineStr"/>
+    </row>
+    <row r="20" ht="58" customHeight="1">
+      <c r="A20" s="19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B20" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$506万
+$25,842/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="C20" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$399万
+$23,738/呎
+(24年-10月)</t>
+        </is>
+      </c>
+      <c r="D20" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$600万
+$24,905/呎
+(26年-03月)</t>
+        </is>
+      </c>
+      <c r="E20" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$596万
+$24,422/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F20" s="21" t="inlineStr"/>
+    </row>
+    <row r="21" ht="58" customHeight="1">
+      <c r="A21" s="19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B21" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$501万
+$25,566/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="C21" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$427万
+$25,411/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D21" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$594万
+$24,660/呎
+(26年-04月)</t>
+        </is>
+      </c>
+      <c r="E21" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$602万
+$24,660/呎
+(26年-05月)</t>
+        </is>
+      </c>
+      <c r="F21" s="21" t="inlineStr"/>
+    </row>
+    <row r="22" ht="58" customHeight="1">
+      <c r="A22" s="19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B22" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$478万
+$24,362/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C22" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$410万
+$24,429/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D22" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$566万
+$23,481/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E22" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$573万
+$23,484/呎
+(25年-06月)</t>
+        </is>
+      </c>
+      <c r="F22" s="21" t="inlineStr"/>
+    </row>
+    <row r="23" ht="58" customHeight="1">
+      <c r="A23" s="19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$464万
+$23,653/呎
+(24年-12月)</t>
+        </is>
+      </c>
+      <c r="C23" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$419万
+$24,917/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D23" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$560万
+$23,257/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E23" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$579万
+$23,725/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F23" s="21" t="inlineStr"/>
+    </row>
+    <row r="24" ht="58" customHeight="1">
+      <c r="A24" s="19" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B24" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$461万
+$23,541/呎
+(25年-08月)</t>
+        </is>
+      </c>
+      <c r="C24" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$404万
+$24,071/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="D24" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$580万
+$24,079/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E24" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$565万
+$23,148/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="F24" s="21" t="inlineStr"/>
+    </row>
+    <row r="25" ht="58" customHeight="1">
+      <c r="A25" s="19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B25" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$473万
+$24,128/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="C25" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$410万
+$24,429/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D25" s="23" t="inlineStr">
+        <is>
+          <t>C | 241呎 (开放式)
+$572万
+$23,734/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="E25" s="23" t="inlineStr">
+        <is>
+          <t>D | 244呎 (开放式)
+$557万
+$22,816/呎
+(25年-07月)</t>
+        </is>
+      </c>
+      <c r="F25" s="21" t="inlineStr"/>
+    </row>
+    <row r="26" ht="58" customHeight="1">
+      <c r="A26" s="19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B26" s="23" t="inlineStr">
+        <is>
+          <t>A | 196呎 (开放式)
+$450万
+$22,980/呎
+(25年-03月)</t>
+        </is>
+      </c>
+      <c r="C26" s="23" t="inlineStr">
+        <is>
+          <t>B | 168呎 (开放式)
+$406万
+$24,185/呎
+(26年-02月)</t>
+        </is>
+      </c>
+      <c r="D26" s="23" t="inlineStr">
+        <is>
+          <t>C | 205呎 (开放式)
+$540万
+$26,322/呎
+(25年-12月)</t>
+        </is>
+      </c>
+      <c r="E26" s="23" t="inlineStr">
+        <is>
+          <t>D | 209呎 (开放式)
+$548万
+$26,196/呎
+(24年-11月)</t>
+        </is>
+      </c>
+      <c r="F26" s="21" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A1:F1"/>
+  </mergeCells>
+  <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
 </file>
--- a/files/港岛-半山区西部-Upper Central.xlsx
+++ b/files/港岛-半山区西部-Upper Central.xlsx
@@ -653,7 +653,7 @@
     <col width="13" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
     <col width="13" customWidth="1" min="7" max="7"/>
-    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
   </cols>

--- a/files/港岛-半山区西部-Upper Central.xlsx
+++ b/files/港岛-半山区西部-Upper Central.xlsx
@@ -643,7 +643,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J87"/>
+  <dimension ref="A1:N87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="27" customWidth="1" min="1" max="1"/>
@@ -656,6 +656,10 @@
     <col width="13" customWidth="1" min="8" max="8"/>
     <col width="14" customWidth="1" min="9" max="9"/>
     <col width="12" customWidth="1" min="10" max="10"/>
+    <col width="13" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="12" customWidth="1" min="13" max="13"/>
+    <col width="12" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1" ht="40" customHeight="1">
@@ -713,6 +717,26 @@
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
+          <t>最高折扣</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>折实总价 (港币)</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="inlineStr">
+        <is>
+          <t>折实呎价 (港币/呎)</t>
+        </is>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>付款办法</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
           <t>是否招标</t>
         </is>
       </c>
@@ -759,6 +783,22 @@
       </c>
       <c r="J3" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K3" s="5" t="n">
+        <v>7532800</v>
+      </c>
+      <c r="L3" s="5" t="n">
+        <v>30872</v>
+      </c>
+      <c r="M3" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N3" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -805,6 +845,22 @@
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K4" s="5" t="n">
+        <v>7467680</v>
+      </c>
+      <c r="L4" s="5" t="n">
+        <v>30858</v>
+      </c>
+      <c r="M4" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N4" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -851,6 +907,22 @@
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>4569840</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>29294</v>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -897,6 +969,22 @@
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K6" s="5" t="n">
+        <v>5287040</v>
+      </c>
+      <c r="L6" s="5" t="n">
+        <v>29870</v>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N6" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -943,6 +1031,22 @@
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K7" s="5" t="n">
+        <v>8602880</v>
+      </c>
+      <c r="L7" s="5" t="n">
+        <v>35549</v>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N7" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -989,6 +1093,22 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>8528080</v>
+      </c>
+      <c r="L8" s="5" t="n">
+        <v>35534</v>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1035,6 +1155,22 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>5850240</v>
+      </c>
+      <c r="L9" s="5" t="n">
+        <v>35031</v>
+      </c>
+      <c r="M9" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N9" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1081,6 +1217,22 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K10" s="5" t="n">
+        <v>6929120</v>
+      </c>
+      <c r="L10" s="5" t="n">
+        <v>35902</v>
+      </c>
+      <c r="M10" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N10" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1127,6 +1279,22 @@
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K11" s="5" t="n">
+        <v>12566000</v>
+      </c>
+      <c r="L11" s="5" t="n">
+        <v>32303</v>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1173,6 +1341,22 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K12" s="5" t="n">
+        <v>8020320</v>
+      </c>
+      <c r="L12" s="5" t="n">
+        <v>32870</v>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1219,6 +1403,22 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>6407280</v>
+      </c>
+      <c r="L13" s="5" t="n">
+        <v>32524</v>
+      </c>
+      <c r="M13" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N13" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1265,6 +1465,22 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>11809000</v>
+      </c>
+      <c r="L14" s="5" t="n">
+        <v>30357</v>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1311,6 +1527,22 @@
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>6984000</v>
+      </c>
+      <c r="L15" s="5" t="n">
+        <v>28623</v>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N15" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1357,6 +1589,22 @@
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>6320160</v>
+      </c>
+      <c r="L16" s="5" t="n">
+        <v>32411</v>
+      </c>
+      <c r="M16" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N16" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1403,6 +1651,22 @@
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K17" s="5" t="n">
+        <v>11704000</v>
+      </c>
+      <c r="L17" s="5" t="n">
+        <v>30087</v>
+      </c>
+      <c r="M17" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N17" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1449,6 +1713,22 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K18" s="5" t="n">
+        <v>6921000</v>
+      </c>
+      <c r="L18" s="5" t="n">
+        <v>28365</v>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1495,6 +1775,22 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K19" s="5" t="n">
+        <v>6264000</v>
+      </c>
+      <c r="L19" s="5" t="n">
+        <v>31797</v>
+      </c>
+      <c r="M19" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N19" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1541,6 +1837,22 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
+          <t>12%</t>
+        </is>
+      </c>
+      <c r="K20" s="5" t="n">
+        <v>7419280</v>
+      </c>
+      <c r="L20" s="5" t="n">
+        <v>30407</v>
+      </c>
+      <c r="M20" s="3" t="inlineStr">
+        <is>
+          <t>90天現金付款計劃</t>
+        </is>
+      </c>
+      <c r="N20" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1587,6 +1899,22 @@
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K21" s="5" t="n">
+        <v>6775000</v>
+      </c>
+      <c r="L21" s="5" t="n">
+        <v>28112</v>
+      </c>
+      <c r="M21" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N21" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1633,6 +1961,22 @@
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K22" s="5" t="n">
+        <v>4704000</v>
+      </c>
+      <c r="L22" s="5" t="n">
+        <v>28000</v>
+      </c>
+      <c r="M22" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N22" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1679,6 +2023,22 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K23" s="5" t="n">
+        <v>5887000</v>
+      </c>
+      <c r="L23" s="5" t="n">
+        <v>30036</v>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1725,6 +2085,22 @@
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K24" s="5" t="n">
+        <v>6890000</v>
+      </c>
+      <c r="L24" s="5" t="n">
+        <v>28471</v>
+      </c>
+      <c r="M24" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N24" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1771,6 +2147,22 @@
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K25" s="5" t="n">
+        <v>6606000</v>
+      </c>
+      <c r="L25" s="5" t="n">
+        <v>27411</v>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1817,6 +2209,22 @@
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K26" s="5" t="n">
+        <v>4359000</v>
+      </c>
+      <c r="L26" s="5" t="n">
+        <v>25946</v>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1863,6 +2271,22 @@
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K27" s="5" t="n">
+        <v>5628000</v>
+      </c>
+      <c r="L27" s="5" t="n">
+        <v>28714</v>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N27" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1909,6 +2333,22 @@
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K28" s="5" t="n">
+        <v>6624000</v>
+      </c>
+      <c r="L28" s="5" t="n">
+        <v>27148</v>
+      </c>
+      <c r="M28" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N28" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -1955,6 +2395,22 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K29" s="5" t="n">
+        <v>6739000</v>
+      </c>
+      <c r="L29" s="5" t="n">
+        <v>27963</v>
+      </c>
+      <c r="M29" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N29" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2001,6 +2457,22 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K30" s="5" t="n">
+        <v>4316000</v>
+      </c>
+      <c r="L30" s="5" t="n">
+        <v>25690</v>
+      </c>
+      <c r="M30" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N30" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2047,6 +2519,22 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K31" s="5" t="n">
+        <v>5154000</v>
+      </c>
+      <c r="L31" s="5" t="n">
+        <v>26296</v>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2093,6 +2581,22 @@
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K32" s="5" t="n">
+        <v>6249000</v>
+      </c>
+      <c r="L32" s="5" t="n">
+        <v>25611</v>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2139,6 +2643,22 @@
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K33" s="5" t="n">
+        <v>6171000</v>
+      </c>
+      <c r="L33" s="5" t="n">
+        <v>25606</v>
+      </c>
+      <c r="M33" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2185,6 +2705,22 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K34" s="5" t="n">
+        <v>4623000</v>
+      </c>
+      <c r="L34" s="5" t="n">
+        <v>27518</v>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2231,6 +2767,22 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K35" s="5" t="n">
+        <v>5360000</v>
+      </c>
+      <c r="L35" s="5" t="n">
+        <v>27347</v>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2277,6 +2829,22 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K36" s="5" t="n">
+        <v>6437000</v>
+      </c>
+      <c r="L36" s="5" t="n">
+        <v>26381</v>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2323,6 +2891,22 @@
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K37" s="5" t="n">
+        <v>6113000</v>
+      </c>
+      <c r="L37" s="5" t="n">
+        <v>25365</v>
+      </c>
+      <c r="M37" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N37" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2369,6 +2953,22 @@
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K38" s="5" t="n">
+        <v>4232000</v>
+      </c>
+      <c r="L38" s="5" t="n">
+        <v>25190</v>
+      </c>
+      <c r="M38" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N38" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2415,6 +3015,22 @@
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K39" s="5" t="n">
+        <v>5158000</v>
+      </c>
+      <c r="L39" s="5" t="n">
+        <v>26316</v>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2461,6 +3077,22 @@
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K40" s="5" t="n">
+        <v>6375000</v>
+      </c>
+      <c r="L40" s="5" t="n">
+        <v>26127</v>
+      </c>
+      <c r="M40" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2507,6 +3139,22 @@
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K41" s="5" t="n">
+        <v>6054000</v>
+      </c>
+      <c r="L41" s="5" t="n">
+        <v>25120</v>
+      </c>
+      <c r="M41" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N41" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2553,6 +3201,22 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K42" s="5" t="n">
+        <v>4401000</v>
+      </c>
+      <c r="L42" s="5" t="n">
+        <v>26196</v>
+      </c>
+      <c r="M42" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N42" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2599,6 +3263,22 @@
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K43" s="5" t="n">
+        <v>5009000</v>
+      </c>
+      <c r="L43" s="5" t="n">
+        <v>25556</v>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2645,6 +3325,22 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K44" s="5" t="n">
+        <v>6347000</v>
+      </c>
+      <c r="L44" s="5" t="n">
+        <v>26012</v>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2691,6 +3387,22 @@
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K45" s="5" t="n">
+        <v>6267000</v>
+      </c>
+      <c r="L45" s="5" t="n">
+        <v>26004</v>
+      </c>
+      <c r="M45" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N45" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2737,6 +3449,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K46" s="5" t="n">
+        <v>4170000</v>
+      </c>
+      <c r="L46" s="5" t="n">
+        <v>24821</v>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2783,6 +3511,22 @@
       </c>
       <c r="J47" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K47" s="5" t="n">
+        <v>5085000</v>
+      </c>
+      <c r="L47" s="5" t="n">
+        <v>25944</v>
+      </c>
+      <c r="M47" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N47" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2829,6 +3573,22 @@
       </c>
       <c r="J48" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K48" s="5" t="n">
+        <v>6014000</v>
+      </c>
+      <c r="L48" s="5" t="n">
+        <v>24648</v>
+      </c>
+      <c r="M48" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N48" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2875,6 +3635,22 @@
       </c>
       <c r="J49" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K49" s="5" t="n">
+        <v>6177000</v>
+      </c>
+      <c r="L49" s="5" t="n">
+        <v>25631</v>
+      </c>
+      <c r="M49" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N49" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2921,6 +3697,22 @@
       </c>
       <c r="J50" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K50" s="5" t="n">
+        <v>4442000</v>
+      </c>
+      <c r="L50" s="5" t="n">
+        <v>26440</v>
+      </c>
+      <c r="M50" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -2967,6 +3759,22 @@
       </c>
       <c r="J51" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K51" s="5" t="n">
+        <v>5011000</v>
+      </c>
+      <c r="L51" s="5" t="n">
+        <v>25566</v>
+      </c>
+      <c r="M51" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N51" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3013,6 +3821,22 @@
       </c>
       <c r="J52" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K52" s="5" t="n">
+        <v>5956000</v>
+      </c>
+      <c r="L52" s="5" t="n">
+        <v>24410</v>
+      </c>
+      <c r="M52" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N52" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3059,6 +3883,22 @@
       </c>
       <c r="J53" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K53" s="5" t="n">
+        <v>5882000</v>
+      </c>
+      <c r="L53" s="5" t="n">
+        <v>24407</v>
+      </c>
+      <c r="M53" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N53" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3105,6 +3945,22 @@
       </c>
       <c r="J54" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K54" s="5" t="n">
+        <v>4068000</v>
+      </c>
+      <c r="L54" s="5" t="n">
+        <v>24214</v>
+      </c>
+      <c r="M54" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N54" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3151,6 +4007,22 @@
       </c>
       <c r="J55" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K55" s="5" t="n">
+        <v>4866000</v>
+      </c>
+      <c r="L55" s="5" t="n">
+        <v>24827</v>
+      </c>
+      <c r="M55" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N55" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3197,6 +4069,22 @@
       </c>
       <c r="J56" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K56" s="5" t="n">
+        <v>5899000</v>
+      </c>
+      <c r="L56" s="5" t="n">
+        <v>24176</v>
+      </c>
+      <c r="M56" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N56" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3243,6 +4131,22 @@
       </c>
       <c r="J57" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K57" s="5" t="n">
+        <v>6060000</v>
+      </c>
+      <c r="L57" s="5" t="n">
+        <v>25145</v>
+      </c>
+      <c r="M57" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N57" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3289,6 +4193,22 @@
       </c>
       <c r="J58" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K58" s="5" t="n">
+        <v>4355000</v>
+      </c>
+      <c r="L58" s="5" t="n">
+        <v>25923</v>
+      </c>
+      <c r="M58" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N58" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3335,6 +4255,22 @@
       </c>
       <c r="J59" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K59" s="5" t="n">
+        <v>4915000</v>
+      </c>
+      <c r="L59" s="5" t="n">
+        <v>25077</v>
+      </c>
+      <c r="M59" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N59" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3381,6 +4317,22 @@
       </c>
       <c r="J60" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K60" s="5" t="n">
+        <v>5959000</v>
+      </c>
+      <c r="L60" s="5" t="n">
+        <v>24422</v>
+      </c>
+      <c r="M60" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N60" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3427,6 +4379,22 @@
       </c>
       <c r="J61" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K61" s="5" t="n">
+        <v>6002000</v>
+      </c>
+      <c r="L61" s="5" t="n">
+        <v>24905</v>
+      </c>
+      <c r="M61" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N61" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3473,6 +4441,22 @@
       </c>
       <c r="J62" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K62" s="5" t="n">
+        <v>3988000</v>
+      </c>
+      <c r="L62" s="5" t="n">
+        <v>23738</v>
+      </c>
+      <c r="M62" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N62" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3519,6 +4503,22 @@
       </c>
       <c r="J63" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K63" s="5" t="n">
+        <v>5065000</v>
+      </c>
+      <c r="L63" s="5" t="n">
+        <v>25842</v>
+      </c>
+      <c r="M63" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N63" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3565,6 +4565,22 @@
       </c>
       <c r="J64" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K64" s="5" t="n">
+        <v>6017000</v>
+      </c>
+      <c r="L64" s="5" t="n">
+        <v>24660</v>
+      </c>
+      <c r="M64" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3611,6 +4627,22 @@
       </c>
       <c r="J65" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K65" s="5" t="n">
+        <v>5943000</v>
+      </c>
+      <c r="L65" s="5" t="n">
+        <v>24660</v>
+      </c>
+      <c r="M65" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N65" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3657,6 +4689,22 @@
       </c>
       <c r="J66" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K66" s="5" t="n">
+        <v>4269000</v>
+      </c>
+      <c r="L66" s="5" t="n">
+        <v>25411</v>
+      </c>
+      <c r="M66" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N66" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3703,6 +4751,22 @@
       </c>
       <c r="J67" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K67" s="5" t="n">
+        <v>5011000</v>
+      </c>
+      <c r="L67" s="5" t="n">
+        <v>25566</v>
+      </c>
+      <c r="M67" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N67" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3749,6 +4813,22 @@
       </c>
       <c r="J68" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K68" s="5" t="n">
+        <v>5730000</v>
+      </c>
+      <c r="L68" s="5" t="n">
+        <v>23484</v>
+      </c>
+      <c r="M68" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N68" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3795,6 +4875,22 @@
       </c>
       <c r="J69" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K69" s="5" t="n">
+        <v>5659000</v>
+      </c>
+      <c r="L69" s="5" t="n">
+        <v>23481</v>
+      </c>
+      <c r="M69" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N69" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3841,6 +4937,22 @@
       </c>
       <c r="J70" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K70" s="5" t="n">
+        <v>4104000</v>
+      </c>
+      <c r="L70" s="5" t="n">
+        <v>24429</v>
+      </c>
+      <c r="M70" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N70" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3887,6 +4999,22 @@
       </c>
       <c r="J71" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K71" s="5" t="n">
+        <v>4775000</v>
+      </c>
+      <c r="L71" s="5" t="n">
+        <v>24362</v>
+      </c>
+      <c r="M71" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N71" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3933,6 +5061,22 @@
       </c>
       <c r="J72" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K72" s="5" t="n">
+        <v>5789000</v>
+      </c>
+      <c r="L72" s="5" t="n">
+        <v>23725</v>
+      </c>
+      <c r="M72" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N72" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -3979,6 +5123,22 @@
       </c>
       <c r="J73" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K73" s="5" t="n">
+        <v>5605000</v>
+      </c>
+      <c r="L73" s="5" t="n">
+        <v>23257</v>
+      </c>
+      <c r="M73" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N73" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4025,6 +5185,22 @@
       </c>
       <c r="J74" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K74" s="5" t="n">
+        <v>4186000</v>
+      </c>
+      <c r="L74" s="5" t="n">
+        <v>24917</v>
+      </c>
+      <c r="M74" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N74" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4071,6 +5247,22 @@
       </c>
       <c r="J75" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K75" s="5" t="n">
+        <v>4636000</v>
+      </c>
+      <c r="L75" s="5" t="n">
+        <v>23653</v>
+      </c>
+      <c r="M75" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N75" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4117,6 +5309,22 @@
       </c>
       <c r="J76" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K76" s="5" t="n">
+        <v>5648000</v>
+      </c>
+      <c r="L76" s="5" t="n">
+        <v>23148</v>
+      </c>
+      <c r="M76" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N76" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4163,6 +5371,22 @@
       </c>
       <c r="J77" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K77" s="5" t="n">
+        <v>5803000</v>
+      </c>
+      <c r="L77" s="5" t="n">
+        <v>24079</v>
+      </c>
+      <c r="M77" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N77" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4209,6 +5433,22 @@
       </c>
       <c r="J78" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K78" s="5" t="n">
+        <v>4044000</v>
+      </c>
+      <c r="L78" s="5" t="n">
+        <v>24071</v>
+      </c>
+      <c r="M78" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N78" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4255,6 +5495,22 @@
       </c>
       <c r="J79" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K79" s="5" t="n">
+        <v>4614000</v>
+      </c>
+      <c r="L79" s="5" t="n">
+        <v>23541</v>
+      </c>
+      <c r="M79" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N79" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4301,6 +5557,22 @@
       </c>
       <c r="J80" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K80" s="5" t="n">
+        <v>5567000</v>
+      </c>
+      <c r="L80" s="5" t="n">
+        <v>22816</v>
+      </c>
+      <c r="M80" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N80" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4347,6 +5619,22 @@
       </c>
       <c r="J81" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K81" s="5" t="n">
+        <v>5720000</v>
+      </c>
+      <c r="L81" s="5" t="n">
+        <v>23734</v>
+      </c>
+      <c r="M81" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N81" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4393,6 +5681,22 @@
       </c>
       <c r="J82" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K82" s="5" t="n">
+        <v>4104000</v>
+      </c>
+      <c r="L82" s="5" t="n">
+        <v>24429</v>
+      </c>
+      <c r="M82" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N82" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4439,6 +5743,22 @@
       </c>
       <c r="J83" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K83" s="5" t="n">
+        <v>4729000</v>
+      </c>
+      <c r="L83" s="5" t="n">
+        <v>24128</v>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N83" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4485,6 +5805,22 @@
       </c>
       <c r="J84" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K84" s="5" t="n">
+        <v>5475000</v>
+      </c>
+      <c r="L84" s="5" t="n">
+        <v>26196</v>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N84" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4531,6 +5867,22 @@
       </c>
       <c r="J85" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K85" s="5" t="n">
+        <v>5396000</v>
+      </c>
+      <c r="L85" s="5" t="n">
+        <v>26322</v>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N85" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4577,6 +5929,22 @@
       </c>
       <c r="J86" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K86" s="5" t="n">
+        <v>4063000</v>
+      </c>
+      <c r="L86" s="5" t="n">
+        <v>24185</v>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N86" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
@@ -4623,13 +5991,29 @@
       </c>
       <c r="J87" s="3" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="K87" s="5" t="n">
+        <v>4504000</v>
+      </c>
+      <c r="L87" s="5" t="n">
+        <v>22980</v>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N87" s="3" t="inlineStr">
+        <is>
           <t>否</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:J1"/>
+    <mergeCell ref="A1:N1"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.25" bottom="0.25" header="0.1" footer="0.1"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4865,7 +6249,7 @@
           <t>E | 389呎 (2房)
 $1257万
 $32,303/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -4890,7 +6274,7 @@
           <t>D | 244呎 (开放式)
 $698万
 $28,623/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -4898,7 +6282,7 @@
           <t>E | 389呎 (2房)
 $1181万
 $30,357/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -4913,7 +6297,7 @@
           <t>A | 197呎 (开放式)
 $626万
 $31,797/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -4923,7 +6307,7 @@
           <t>D | 244呎 (开放式)
 $692万
 $28,365/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -4931,7 +6315,7 @@
           <t>E | 389呎 (2房)
 $1170万
 $30,087/呎
-(26年-02月)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
     </row>
@@ -4946,7 +6330,7 @@
           <t>A | 196呎 (开放式)
 $589万
 $30,036/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -4954,7 +6338,7 @@
           <t>B | 168呎 (开放式)
 $470万
 $28,000/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -4962,7 +6346,7 @@
           <t>C | 241呎 (开放式)
 $678万
 $28,112/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -4986,7 +6370,7 @@
           <t>A | 196呎 (开放式)
 $563万
 $28,714/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -4994,7 +6378,7 @@
           <t>B | 168呎 (开放式)
 $436万
 $25,946/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -5002,7 +6386,7 @@
           <t>C | 241呎 (开放式)
 $661万
 $27,411/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -5010,7 +6394,7 @@
           <t>D | 242呎 (开放式)
 $689万
 $28,471/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -5026,7 +6410,7 @@
           <t>A | 196呎 (开放式)
 $515万
 $26,296/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -5034,7 +6418,7 @@
           <t>B | 168呎 (开放式)
 $432万
 $25,690/呎
-(25年-03月)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -5042,7 +6426,7 @@
           <t>C | 241呎 (开放式)
 $674万
 $27,963/呎
-(26年-06月)</t>
+(26年-06月-21日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -5050,7 +6434,7 @@
           <t>D | 244呎 (开放式)
 $662万
 $27,148/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -5066,7 +6450,7 @@
           <t>A | 196呎 (开放式)
 $536万
 $27,347/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -5074,7 +6458,7 @@
           <t>B | 168呎 (开放式)
 $462万
 $27,518/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -5082,7 +6466,7 @@
           <t>C | 241呎 (开放式)
 $617万
 $25,606/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -5090,7 +6474,7 @@
           <t>D | 244呎 (开放式)
 $625万
 $25,611/呎
-(25年-01月)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -5106,7 +6490,7 @@
           <t>A | 196呎 (开放式)
 $516万
 $26,316/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -5114,7 +6498,7 @@
           <t>B | 168呎 (开放式)
 $423万
 $25,190/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -5122,7 +6506,7 @@
           <t>C | 241呎 (开放式)
 $611万
 $25,365/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -5130,7 +6514,7 @@
           <t>D | 244呎 (开放式)
 $644万
 $26,381/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -5146,7 +6530,7 @@
           <t>A | 196呎 (开放式)
 $501万
 $25,556/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -5154,7 +6538,7 @@
           <t>B | 168呎 (开放式)
 $440万
 $26,196/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -5162,7 +6546,7 @@
           <t>C | 241呎 (开放式)
 $605万
 $25,120/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -5170,7 +6554,7 @@
           <t>D | 244呎 (开放式)
 $638万
 $26,127/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -5186,7 +6570,7 @@
           <t>A | 196呎 (开放式)
 $508万
 $25,944/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -5194,7 +6578,7 @@
           <t>B | 168呎 (开放式)
 $417万
 $24,821/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -5202,7 +6586,7 @@
           <t>C | 241呎 (开放式)
 $627万
 $26,004/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -5210,7 +6594,7 @@
           <t>D | 244呎 (开放式)
 $635万
 $26,012/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -5226,7 +6610,7 @@
           <t>A | 196呎 (开放式)
 $501万
 $25,566/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -5234,7 +6618,7 @@
           <t>B | 168呎 (开放式)
 $444万
 $26,440/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -5242,7 +6626,7 @@
           <t>C | 241呎 (开放式)
 $618万
 $25,631/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -5250,7 +6634,7 @@
           <t>D | 244呎 (开放式)
 $601万
 $24,648/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr"/>
@@ -5266,7 +6650,7 @@
           <t>A | 196呎 (开放式)
 $487万
 $24,827/呎
-(25年-05月)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -5274,7 +6658,7 @@
           <t>B | 168呎 (开放式)
 $407万
 $24,214/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -5282,7 +6666,7 @@
           <t>C | 241呎 (开放式)
 $588万
 $24,407/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -5290,7 +6674,7 @@
           <t>D | 244呎 (开放式)
 $596万
 $24,410/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr"/>
@@ -5306,7 +6690,7 @@
           <t>A | 196呎 (开放式)
 $492万
 $25,077/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -5314,7 +6698,7 @@
           <t>B | 168呎 (开放式)
 $436万
 $25,923/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -5322,7 +6706,7 @@
           <t>C | 241呎 (开放式)
 $606万
 $25,145/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -5330,7 +6714,7 @@
           <t>D | 244呎 (开放式)
 $590万
 $24,176/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr"/>
@@ -5346,7 +6730,7 @@
           <t>A | 196呎 (开放式)
 $506万
 $25,842/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -5354,7 +6738,7 @@
           <t>B | 168呎 (开放式)
 $399万
 $23,738/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -5362,7 +6746,7 @@
           <t>C | 241呎 (开放式)
 $600万
 $24,905/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -5370,7 +6754,7 @@
           <t>D | 244呎 (开放式)
 $596万
 $24,422/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr"/>
@@ -5386,7 +6770,7 @@
           <t>A | 196呎 (开放式)
 $501万
 $25,566/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -5394,7 +6778,7 @@
           <t>B | 168呎 (开放式)
 $427万
 $25,411/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -5402,7 +6786,7 @@
           <t>C | 241呎 (开放式)
 $594万
 $24,660/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -5410,7 +6794,7 @@
           <t>D | 244呎 (开放式)
 $602万
 $24,660/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr"/>
@@ -5426,7 +6810,7 @@
           <t>A | 196呎 (开放式)
 $478万
 $24,362/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -5434,7 +6818,7 @@
           <t>B | 168呎 (开放式)
 $410万
 $24,429/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -5442,7 +6826,7 @@
           <t>C | 241呎 (开放式)
 $566万
 $23,481/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -5450,7 +6834,7 @@
           <t>D | 244呎 (开放式)
 $573万
 $23,484/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr"/>
@@ -5466,7 +6850,7 @@
           <t>A | 196呎 (开放式)
 $464万
 $23,653/呎
-(24年-12月)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -5474,7 +6858,7 @@
           <t>B | 168呎 (开放式)
 $419万
 $24,917/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -5482,7 +6866,7 @@
           <t>C | 241呎 (开放式)
 $560万
 $23,257/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -5490,7 +6874,7 @@
           <t>D | 244呎 (开放式)
 $579万
 $23,725/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr"/>
@@ -5506,7 +6890,7 @@
           <t>A | 196呎 (开放式)
 $461万
 $23,541/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -5514,7 +6898,7 @@
           <t>B | 168呎 (开放式)
 $404万
 $24,071/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -5522,7 +6906,7 @@
           <t>C | 241呎 (开放式)
 $580万
 $24,079/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -5530,7 +6914,7 @@
           <t>D | 244呎 (开放式)
 $565万
 $23,148/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr"/>
@@ -5546,7 +6930,7 @@
           <t>A | 196呎 (开放式)
 $473万
 $24,128/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -5554,7 +6938,7 @@
           <t>B | 168呎 (开放式)
 $410万
 $24,429/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -5562,7 +6946,7 @@
           <t>C | 241呎 (开放式)
 $572万
 $23,734/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -5570,7 +6954,7 @@
           <t>D | 244呎 (开放式)
 $557万
 $22,816/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr"/>
@@ -5586,7 +6970,7 @@
           <t>A | 196呎 (开放式)
 $450万
 $22,980/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -5594,7 +6978,7 @@
           <t>B | 168呎 (开放式)
 $406万
 $24,185/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -5602,7 +6986,7 @@
           <t>C | 205呎 (开放式)
 $540万
 $26,322/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -5610,7 +6994,7 @@
           <t>D | 209呎 (开放式)
 $548万
 $26,196/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr"/>

--- a/files/港岛-半山区西部-Upper Central.xlsx
+++ b/files/港岛-半山区西部-Upper Central.xlsx
@@ -1764,7 +1764,7 @@
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H19" s="5" t="n">
@@ -2065,7 +2065,7 @@
         </is>
       </c>
       <c r="E24" s="4" t="n">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
@@ -2074,14 +2074,14 @@
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-14</t>
         </is>
       </c>
       <c r="H24" s="5" t="n">
         <v>6890000</v>
       </c>
       <c r="I24" s="5" t="n">
-        <v>28471</v>
+        <v>28238</v>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
@@ -2092,7 +2092,7 @@
         <v>6890000</v>
       </c>
       <c r="L24" s="5" t="n">
-        <v>28471</v>
+        <v>28238</v>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
@@ -2384,7 +2384,7 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t>2026-06-21</t>
+          <t>2026-07-15</t>
         </is>
       </c>
       <c r="H29" s="5" t="n">
@@ -6297,7 +6297,7 @@
           <t>A | 197呎 (开放式)
 $626万
 $31,797/呎
-(26年-06月-21日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -6391,10 +6391,10 @@
       </c>
       <c r="E11" s="23" t="inlineStr">
         <is>
-          <t>D | 242呎 (开放式)
+          <t>D | 244呎 (开放式)
 $689万
-$28,471/呎
-(26年-06月-21日)</t>
+$28,238/呎
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -6426,7 +6426,7 @@
           <t>C | 241呎 (开放式)
 $674万
 $27,963/呎
-(26年-06月-21日)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">

--- a/files/港岛-半山区西部-Upper Central.xlsx
+++ b/files/港岛-半山区西部-Upper Central.xlsx
@@ -6249,7 +6249,7 @@
           <t>E | 389呎 (2房)
 $1257万
 $32,303/呎
-(26年-03月-31日)</t>
+(26年-03月)</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
           <t>D | 244呎 (开放式)
 $698万
 $28,623/呎
-(25年-12月-14日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -6282,7 +6282,7 @@
           <t>E | 389呎 (2房)
 $1181万
 $30,357/呎
-(25年-12月-10日)</t>
+(25年-12月)</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
           <t>A | 197呎 (开放式)
 $626万
 $31,797/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -6307,7 +6307,7 @@
           <t>D | 244呎 (开放式)
 $692万
 $28,365/呎
-(26年-03月-24日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -6315,7 +6315,7 @@
           <t>E | 389呎 (2房)
 $1170万
 $30,087/呎
-(26年-02月-02日)</t>
+(26年-02月)</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
           <t>A | 196呎 (开放式)
 $589万
 $30,036/呎
-(26年-06月-16日)</t>
+(26年-06月)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -6338,7 +6338,7 @@
           <t>B | 168呎 (开放式)
 $470万
 $28,000/呎
-(25年-05月-14日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -6346,7 +6346,7 @@
           <t>C | 241呎 (开放式)
 $678万
 $28,112/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -6370,7 +6370,7 @@
           <t>A | 196呎 (开放式)
 $563万
 $28,714/呎
-(26年-05月-27日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -6378,7 +6378,7 @@
           <t>B | 168呎 (开放式)
 $436万
 $25,946/呎
-(25年-03月-27日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -6386,7 +6386,7 @@
           <t>C | 241呎 (开放式)
 $661万
 $27,411/呎
-(26年-05月-10日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -6394,7 +6394,7 @@
           <t>D | 244呎 (开放式)
 $689万
 $28,238/呎
-(26年-07月-14日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -6410,7 +6410,7 @@
           <t>A | 196呎 (开放式)
 $515万
 $26,296/呎
-(25年-12月-11日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -6418,7 +6418,7 @@
           <t>B | 168呎 (开放式)
 $432万
 $25,690/呎
-(25年-03月-03日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -6426,7 +6426,7 @@
           <t>C | 241呎 (开放式)
 $674万
 $27,963/呎
-(26年-07月-15日)</t>
+(26年-07月)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -6434,7 +6434,7 @@
           <t>D | 244呎 (开放式)
 $662万
 $27,148/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -6450,7 +6450,7 @@
           <t>A | 196呎 (开放式)
 $536万
 $27,347/呎
-(26年-05月-19日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -6458,7 +6458,7 @@
           <t>B | 168呎 (开放式)
 $462万
 $27,518/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -6466,7 +6466,7 @@
           <t>C | 241呎 (开放式)
 $617万
 $25,606/呎
-(25年-12月-08日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -6474,7 +6474,7 @@
           <t>D | 244呎 (开放式)
 $625万
 $25,611/呎
-(25年-01月-13日)</t>
+(25年-01月)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -6490,7 +6490,7 @@
           <t>A | 196呎 (开放式)
 $516万
 $26,316/呎
-(26年-01月-21日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -6498,7 +6498,7 @@
           <t>B | 168呎 (开放式)
 $423万
 $25,190/呎
-(25年-02月-20日)</t>
+(25年-02月)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -6506,7 +6506,7 @@
           <t>C | 241呎 (开放式)
 $611万
 $25,365/呎
-(25年-12月-03日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -6514,7 +6514,7 @@
           <t>D | 244呎 (开放式)
 $644万
 $26,381/呎
-(26年-05月-07日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -6530,7 +6530,7 @@
           <t>A | 196呎 (开放式)
 $501万
 $25,556/呎
-(25年-11月-26日)</t>
+(25年-11月)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -6538,7 +6538,7 @@
           <t>B | 168呎 (开放式)
 $440万
 $26,196/呎
-(25年-12月-17日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -6546,7 +6546,7 @@
           <t>C | 241呎 (开放式)
 $605万
 $25,120/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -6554,7 +6554,7 @@
           <t>D | 244呎 (开放式)
 $638万
 $26,127/呎
-(26年-03月-26日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -6570,7 +6570,7 @@
           <t>A | 196呎 (开放式)
 $508万
 $25,944/呎
-(26年-01月-20日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -6578,7 +6578,7 @@
           <t>B | 168呎 (开放式)
 $417万
 $24,821/呎
-(24年-11月-04日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -6586,7 +6586,7 @@
           <t>C | 241呎 (开放式)
 $627万
 $26,004/呎
-(26年-05月-28日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -6594,7 +6594,7 @@
           <t>D | 244呎 (开放式)
 $635万
 $26,012/呎
-(26年-02月-12日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -6610,7 +6610,7 @@
           <t>A | 196呎 (开放式)
 $501万
 $25,566/呎
-(26年-01月-05日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -6618,7 +6618,7 @@
           <t>B | 168呎 (开放式)
 $444万
 $26,440/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -6626,7 +6626,7 @@
           <t>C | 241呎 (开放式)
 $618万
 $25,631/呎
-(26年-04月-23日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -6634,7 +6634,7 @@
           <t>D | 244呎 (开放式)
 $601万
 $24,648/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr"/>
@@ -6650,7 +6650,7 @@
           <t>A | 196呎 (开放式)
 $487万
 $24,827/呎
-(25年-05月-26日)</t>
+(25年-05月)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -6658,7 +6658,7 @@
           <t>B | 168呎 (开放式)
 $407万
 $24,214/呎
-(24年-10月-27日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -6666,7 +6666,7 @@
           <t>C | 241呎 (开放式)
 $588万
 $24,407/呎
-(26年-01月-26日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -6674,7 +6674,7 @@
           <t>D | 244呎 (开放式)
 $596万
 $24,410/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr"/>
@@ -6690,7 +6690,7 @@
           <t>A | 196呎 (开放式)
 $492万
 $25,077/呎
-(25年-12月-30日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -6698,7 +6698,7 @@
           <t>B | 168呎 (开放式)
 $436万
 $25,923/呎
-(26年-02月-11日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -6706,7 +6706,7 @@
           <t>C | 241呎 (开放式)
 $606万
 $25,145/呎
-(26年-03月-10日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -6714,7 +6714,7 @@
           <t>D | 244呎 (开放式)
 $590万
 $24,176/呎
-(26年-01月-06日)</t>
+(26年-01月)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr"/>
@@ -6730,7 +6730,7 @@
           <t>A | 196呎 (开放式)
 $506万
 $25,842/呎
-(26年-02月-10日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -6738,7 +6738,7 @@
           <t>B | 168呎 (开放式)
 $399万
 $23,738/呎
-(24年-10月-15日)</t>
+(24年-10月)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -6746,7 +6746,7 @@
           <t>C | 241呎 (开放式)
 $600万
 $24,905/呎
-(26年-03月-16日)</t>
+(26年-03月)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -6754,7 +6754,7 @@
           <t>D | 244呎 (开放式)
 $596万
 $24,422/呎
-(26年-02月-26日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr"/>
@@ -6770,7 +6770,7 @@
           <t>A | 196呎 (开放式)
 $501万
 $25,566/呎
-(26年-04月-16日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -6778,7 +6778,7 @@
           <t>B | 168呎 (开放式)
 $427万
 $25,411/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -6786,7 +6786,7 @@
           <t>C | 241呎 (开放式)
 $594万
 $24,660/呎
-(26年-04月-19日)</t>
+(26年-04月)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -6794,7 +6794,7 @@
           <t>D | 244呎 (开放式)
 $602万
 $24,660/呎
-(26年-05月-06日)</t>
+(26年-05月)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr"/>
@@ -6810,7 +6810,7 @@
           <t>A | 196呎 (开放式)
 $478万
 $24,362/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -6818,7 +6818,7 @@
           <t>B | 168呎 (开放式)
 $410万
 $24,429/呎
-(25年-12月-21日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -6826,7 +6826,7 @@
           <t>C | 241呎 (开放式)
 $566万
 $23,481/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -6834,7 +6834,7 @@
           <t>D | 244呎 (开放式)
 $573万
 $23,484/呎
-(25年-06月-12日)</t>
+(25年-06月)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr"/>
@@ -6850,7 +6850,7 @@
           <t>A | 196呎 (开放式)
 $464万
 $23,653/呎
-(24年-12月-17日)</t>
+(24年-12月)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -6858,7 +6858,7 @@
           <t>B | 168呎 (开放式)
 $419万
 $24,917/呎
-(26年-02月-19日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -6866,7 +6866,7 @@
           <t>C | 241呎 (开放式)
 $560万
 $23,257/呎
-(25年-12月-01日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -6874,7 +6874,7 @@
           <t>D | 244呎 (开放式)
 $579万
 $23,725/呎
-(26年-02月-08日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr"/>
@@ -6890,7 +6890,7 @@
           <t>A | 196呎 (开放式)
 $461万
 $23,541/呎
-(25年-08月-20日)</t>
+(25年-08月)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -6898,7 +6898,7 @@
           <t>B | 168呎 (开放式)
 $404万
 $24,071/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -6906,7 +6906,7 @@
           <t>C | 241呎 (开放式)
 $580万
 $24,079/呎
-(26年-02月-23日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -6914,7 +6914,7 @@
           <t>D | 244呎 (开放式)
 $565万
 $23,148/呎
-(26年-02月-09日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr"/>
@@ -6930,7 +6930,7 @@
           <t>A | 196呎 (开放式)
 $473万
 $24,128/呎
-(25年-12月-29日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -6938,7 +6938,7 @@
           <t>B | 168呎 (开放式)
 $410万
 $24,429/呎
-(26年-02月-01日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -6946,7 +6946,7 @@
           <t>C | 241呎 (开放式)
 $572万
 $23,734/呎
-(26年-02月-24日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -6954,7 +6954,7 @@
           <t>D | 244呎 (开放式)
 $557万
 $22,816/呎
-(25年-07月-13日)</t>
+(25年-07月)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr"/>
@@ -6970,7 +6970,7 @@
           <t>A | 196呎 (开放式)
 $450万
 $22,980/呎
-(25年-03月-30日)</t>
+(25年-03月)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -6978,7 +6978,7 @@
           <t>B | 168呎 (开放式)
 $406万
 $24,185/呎
-(26年-02月-05日)</t>
+(26年-02月)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -6986,7 +6986,7 @@
           <t>C | 205呎 (开放式)
 $540万
 $26,322/呎
-(25年-12月-18日)</t>
+(25年-12月)</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -6994,7 +6994,7 @@
           <t>D | 209呎 (开放式)
 $548万
 $26,196/呎
-(24年-11月-18日)</t>
+(24年-11月)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr"/>

--- a/files/港岛-半山区西部-Upper Central.xlsx
+++ b/files/港岛-半山区西部-Upper Central.xlsx
@@ -6249,7 +6249,7 @@
           <t>E | 389呎 (2房)
 $1257万
 $32,303/呎
-(26年-03月)</t>
+(26年-03月-31日)</t>
         </is>
       </c>
     </row>
@@ -6274,7 +6274,7 @@
           <t>D | 244呎 (开放式)
 $698万
 $28,623/呎
-(25年-12月)</t>
+(25年-12月-14日)</t>
         </is>
       </c>
       <c r="F8" s="23" t="inlineStr">
@@ -6282,7 +6282,7 @@
           <t>E | 389呎 (2房)
 $1181万
 $30,357/呎
-(25年-12月)</t>
+(25年-12月-10日)</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6297,7 @@
           <t>A | 197呎 (开放式)
 $626万
 $31,797/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="C9" s="21" t="inlineStr"/>
@@ -6307,7 +6307,7 @@
           <t>D | 244呎 (开放式)
 $692万
 $28,365/呎
-(26年-03月)</t>
+(26年-03月-24日)</t>
         </is>
       </c>
       <c r="F9" s="23" t="inlineStr">
@@ -6315,7 +6315,7 @@
           <t>E | 389呎 (2房)
 $1170万
 $30,087/呎
-(26年-02月)</t>
+(26年-02月-02日)</t>
         </is>
       </c>
     </row>
@@ -6330,7 +6330,7 @@
           <t>A | 196呎 (开放式)
 $589万
 $30,036/呎
-(26年-06月)</t>
+(26年-06月-16日)</t>
         </is>
       </c>
       <c r="C10" s="23" t="inlineStr">
@@ -6338,7 +6338,7 @@
           <t>B | 168呎 (开放式)
 $470万
 $28,000/呎
-(25年-05月)</t>
+(25年-05月-14日)</t>
         </is>
       </c>
       <c r="D10" s="23" t="inlineStr">
@@ -6346,7 +6346,7 @@
           <t>C | 241呎 (开放式)
 $678万
 $28,112/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="E10" s="22" t="inlineStr">
@@ -6370,7 +6370,7 @@
           <t>A | 196呎 (开放式)
 $563万
 $28,714/呎
-(26年-05月)</t>
+(26年-05月-27日)</t>
         </is>
       </c>
       <c r="C11" s="23" t="inlineStr">
@@ -6378,7 +6378,7 @@
           <t>B | 168呎 (开放式)
 $436万
 $25,946/呎
-(25年-03月)</t>
+(25年-03月-27日)</t>
         </is>
       </c>
       <c r="D11" s="23" t="inlineStr">
@@ -6386,7 +6386,7 @@
           <t>C | 241呎 (开放式)
 $661万
 $27,411/呎
-(26年-05月)</t>
+(26年-05月-10日)</t>
         </is>
       </c>
       <c r="E11" s="23" t="inlineStr">
@@ -6394,7 +6394,7 @@
           <t>D | 244呎 (开放式)
 $689万
 $28,238/呎
-(26年-07月)</t>
+(26年-07月-14日)</t>
         </is>
       </c>
       <c r="F11" s="21" t="inlineStr"/>
@@ -6410,7 +6410,7 @@
           <t>A | 196呎 (开放式)
 $515万
 $26,296/呎
-(25年-12月)</t>
+(25年-12月-11日)</t>
         </is>
       </c>
       <c r="C12" s="23" t="inlineStr">
@@ -6418,7 +6418,7 @@
           <t>B | 168呎 (开放式)
 $432万
 $25,690/呎
-(25年-03月)</t>
+(25年-03月-03日)</t>
         </is>
       </c>
       <c r="D12" s="23" t="inlineStr">
@@ -6426,7 +6426,7 @@
           <t>C | 241呎 (开放式)
 $674万
 $27,963/呎
-(26年-07月)</t>
+(26年-07月-15日)</t>
         </is>
       </c>
       <c r="E12" s="23" t="inlineStr">
@@ -6434,7 +6434,7 @@
           <t>D | 244呎 (开放式)
 $662万
 $27,148/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="F12" s="21" t="inlineStr"/>
@@ -6450,7 +6450,7 @@
           <t>A | 196呎 (开放式)
 $536万
 $27,347/呎
-(26年-05月)</t>
+(26年-05月-19日)</t>
         </is>
       </c>
       <c r="C13" s="23" t="inlineStr">
@@ -6458,7 +6458,7 @@
           <t>B | 168呎 (开放式)
 $462万
 $27,518/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="D13" s="23" t="inlineStr">
@@ -6466,7 +6466,7 @@
           <t>C | 241呎 (开放式)
 $617万
 $25,606/呎
-(25年-12月)</t>
+(25年-12月-08日)</t>
         </is>
       </c>
       <c r="E13" s="23" t="inlineStr">
@@ -6474,7 +6474,7 @@
           <t>D | 244呎 (开放式)
 $625万
 $25,611/呎
-(25年-01月)</t>
+(25年-01月-13日)</t>
         </is>
       </c>
       <c r="F13" s="21" t="inlineStr"/>
@@ -6490,7 +6490,7 @@
           <t>A | 196呎 (开放式)
 $516万
 $26,316/呎
-(26年-01月)</t>
+(26年-01月-21日)</t>
         </is>
       </c>
       <c r="C14" s="23" t="inlineStr">
@@ -6498,7 +6498,7 @@
           <t>B | 168呎 (开放式)
 $423万
 $25,190/呎
-(25年-02月)</t>
+(25年-02月-20日)</t>
         </is>
       </c>
       <c r="D14" s="23" t="inlineStr">
@@ -6506,7 +6506,7 @@
           <t>C | 241呎 (开放式)
 $611万
 $25,365/呎
-(25年-12月)</t>
+(25年-12月-03日)</t>
         </is>
       </c>
       <c r="E14" s="23" t="inlineStr">
@@ -6514,7 +6514,7 @@
           <t>D | 244呎 (开放式)
 $644万
 $26,381/呎
-(26年-05月)</t>
+(26年-05月-07日)</t>
         </is>
       </c>
       <c r="F14" s="21" t="inlineStr"/>
@@ -6530,7 +6530,7 @@
           <t>A | 196呎 (开放式)
 $501万
 $25,556/呎
-(25年-11月)</t>
+(25年-11月-26日)</t>
         </is>
       </c>
       <c r="C15" s="23" t="inlineStr">
@@ -6538,7 +6538,7 @@
           <t>B | 168呎 (开放式)
 $440万
 $26,196/呎
-(25年-12月)</t>
+(25年-12月-17日)</t>
         </is>
       </c>
       <c r="D15" s="23" t="inlineStr">
@@ -6546,7 +6546,7 @@
           <t>C | 241呎 (开放式)
 $605万
 $25,120/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="E15" s="23" t="inlineStr">
@@ -6554,7 +6554,7 @@
           <t>D | 244呎 (开放式)
 $638万
 $26,127/呎
-(26年-03月)</t>
+(26年-03月-26日)</t>
         </is>
       </c>
       <c r="F15" s="21" t="inlineStr"/>
@@ -6570,7 +6570,7 @@
           <t>A | 196呎 (开放式)
 $508万
 $25,944/呎
-(26年-01月)</t>
+(26年-01月-20日)</t>
         </is>
       </c>
       <c r="C16" s="23" t="inlineStr">
@@ -6578,7 +6578,7 @@
           <t>B | 168呎 (开放式)
 $417万
 $24,821/呎
-(24年-11月)</t>
+(24年-11月-04日)</t>
         </is>
       </c>
       <c r="D16" s="23" t="inlineStr">
@@ -6586,7 +6586,7 @@
           <t>C | 241呎 (开放式)
 $627万
 $26,004/呎
-(26年-05月)</t>
+(26年-05月-28日)</t>
         </is>
       </c>
       <c r="E16" s="23" t="inlineStr">
@@ -6594,7 +6594,7 @@
           <t>D | 244呎 (开放式)
 $635万
 $26,012/呎
-(26年-02月)</t>
+(26年-02月-12日)</t>
         </is>
       </c>
       <c r="F16" s="21" t="inlineStr"/>
@@ -6610,7 +6610,7 @@
           <t>A | 196呎 (开放式)
 $501万
 $25,566/呎
-(26年-01月)</t>
+(26年-01月-05日)</t>
         </is>
       </c>
       <c r="C17" s="23" t="inlineStr">
@@ -6618,7 +6618,7 @@
           <t>B | 168呎 (开放式)
 $444万
 $26,440/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="D17" s="23" t="inlineStr">
@@ -6626,7 +6626,7 @@
           <t>C | 241呎 (开放式)
 $618万
 $25,631/呎
-(26年-04月)</t>
+(26年-04月-23日)</t>
         </is>
       </c>
       <c r="E17" s="23" t="inlineStr">
@@ -6634,7 +6634,7 @@
           <t>D | 244呎 (开放式)
 $601万
 $24,648/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="F17" s="21" t="inlineStr"/>
@@ -6650,7 +6650,7 @@
           <t>A | 196呎 (开放式)
 $487万
 $24,827/呎
-(25年-05月)</t>
+(25年-05月-26日)</t>
         </is>
       </c>
       <c r="C18" s="23" t="inlineStr">
@@ -6658,7 +6658,7 @@
           <t>B | 168呎 (开放式)
 $407万
 $24,214/呎
-(24年-10月)</t>
+(24年-10月-27日)</t>
         </is>
       </c>
       <c r="D18" s="23" t="inlineStr">
@@ -6666,7 +6666,7 @@
           <t>C | 241呎 (开放式)
 $588万
 $24,407/呎
-(26年-01月)</t>
+(26年-01月-26日)</t>
         </is>
       </c>
       <c r="E18" s="23" t="inlineStr">
@@ -6674,7 +6674,7 @@
           <t>D | 244呎 (开放式)
 $596万
 $24,410/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="F18" s="21" t="inlineStr"/>
@@ -6690,7 +6690,7 @@
           <t>A | 196呎 (开放式)
 $492万
 $25,077/呎
-(25年-12月)</t>
+(25年-12月-30日)</t>
         </is>
       </c>
       <c r="C19" s="23" t="inlineStr">
@@ -6698,7 +6698,7 @@
           <t>B | 168呎 (开放式)
 $436万
 $25,923/呎
-(26年-02月)</t>
+(26年-02月-11日)</t>
         </is>
       </c>
       <c r="D19" s="23" t="inlineStr">
@@ -6706,7 +6706,7 @@
           <t>C | 241呎 (开放式)
 $606万
 $25,145/呎
-(26年-03月)</t>
+(26年-03月-10日)</t>
         </is>
       </c>
       <c r="E19" s="23" t="inlineStr">
@@ -6714,7 +6714,7 @@
           <t>D | 244呎 (开放式)
 $590万
 $24,176/呎
-(26年-01月)</t>
+(26年-01月-06日)</t>
         </is>
       </c>
       <c r="F19" s="21" t="inlineStr"/>
@@ -6730,7 +6730,7 @@
           <t>A | 196呎 (开放式)
 $506万
 $25,842/呎
-(26年-02月)</t>
+(26年-02月-10日)</t>
         </is>
       </c>
       <c r="C20" s="23" t="inlineStr">
@@ -6738,7 +6738,7 @@
           <t>B | 168呎 (开放式)
 $399万
 $23,738/呎
-(24年-10月)</t>
+(24年-10月-15日)</t>
         </is>
       </c>
       <c r="D20" s="23" t="inlineStr">
@@ -6746,7 +6746,7 @@
           <t>C | 241呎 (开放式)
 $600万
 $24,905/呎
-(26年-03月)</t>
+(26年-03月-16日)</t>
         </is>
       </c>
       <c r="E20" s="23" t="inlineStr">
@@ -6754,7 +6754,7 @@
           <t>D | 244呎 (开放式)
 $596万
 $24,422/呎
-(26年-02月)</t>
+(26年-02月-26日)</t>
         </is>
       </c>
       <c r="F20" s="21" t="inlineStr"/>
@@ -6770,7 +6770,7 @@
           <t>A | 196呎 (开放式)
 $501万
 $25,566/呎
-(26年-04月)</t>
+(26年-04月-16日)</t>
         </is>
       </c>
       <c r="C21" s="23" t="inlineStr">
@@ -6778,7 +6778,7 @@
           <t>B | 168呎 (开放式)
 $427万
 $25,411/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D21" s="23" t="inlineStr">
@@ -6786,7 +6786,7 @@
           <t>C | 241呎 (开放式)
 $594万
 $24,660/呎
-(26年-04月)</t>
+(26年-04月-19日)</t>
         </is>
       </c>
       <c r="E21" s="23" t="inlineStr">
@@ -6794,7 +6794,7 @@
           <t>D | 244呎 (开放式)
 $602万
 $24,660/呎
-(26年-05月)</t>
+(26年-05月-06日)</t>
         </is>
       </c>
       <c r="F21" s="21" t="inlineStr"/>
@@ -6810,7 +6810,7 @@
           <t>A | 196呎 (开放式)
 $478万
 $24,362/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="C22" s="23" t="inlineStr">
@@ -6818,7 +6818,7 @@
           <t>B | 168呎 (开放式)
 $410万
 $24,429/呎
-(25年-12月)</t>
+(25年-12月-21日)</t>
         </is>
       </c>
       <c r="D22" s="23" t="inlineStr">
@@ -6826,7 +6826,7 @@
           <t>C | 241呎 (开放式)
 $566万
 $23,481/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="E22" s="23" t="inlineStr">
@@ -6834,7 +6834,7 @@
           <t>D | 244呎 (开放式)
 $573万
 $23,484/呎
-(25年-06月)</t>
+(25年-06月-12日)</t>
         </is>
       </c>
       <c r="F22" s="21" t="inlineStr"/>
@@ -6850,7 +6850,7 @@
           <t>A | 196呎 (开放式)
 $464万
 $23,653/呎
-(24年-12月)</t>
+(24年-12月-17日)</t>
         </is>
       </c>
       <c r="C23" s="23" t="inlineStr">
@@ -6858,7 +6858,7 @@
           <t>B | 168呎 (开放式)
 $419万
 $24,917/呎
-(26年-02月)</t>
+(26年-02月-19日)</t>
         </is>
       </c>
       <c r="D23" s="23" t="inlineStr">
@@ -6866,7 +6866,7 @@
           <t>C | 241呎 (开放式)
 $560万
 $23,257/呎
-(25年-12月)</t>
+(25年-12月-01日)</t>
         </is>
       </c>
       <c r="E23" s="23" t="inlineStr">
@@ -6874,7 +6874,7 @@
           <t>D | 244呎 (开放式)
 $579万
 $23,725/呎
-(26年-02月)</t>
+(26年-02月-08日)</t>
         </is>
       </c>
       <c r="F23" s="21" t="inlineStr"/>
@@ -6890,7 +6890,7 @@
           <t>A | 196呎 (开放式)
 $461万
 $23,541/呎
-(25年-08月)</t>
+(25年-08月-20日)</t>
         </is>
       </c>
       <c r="C24" s="23" t="inlineStr">
@@ -6898,7 +6898,7 @@
           <t>B | 168呎 (开放式)
 $404万
 $24,071/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="D24" s="23" t="inlineStr">
@@ -6906,7 +6906,7 @@
           <t>C | 241呎 (开放式)
 $580万
 $24,079/呎
-(26年-02月)</t>
+(26年-02月-23日)</t>
         </is>
       </c>
       <c r="E24" s="23" t="inlineStr">
@@ -6914,7 +6914,7 @@
           <t>D | 244呎 (开放式)
 $565万
 $23,148/呎
-(26年-02月)</t>
+(26年-02月-09日)</t>
         </is>
       </c>
       <c r="F24" s="21" t="inlineStr"/>
@@ -6930,7 +6930,7 @@
           <t>A | 196呎 (开放式)
 $473万
 $24,128/呎
-(25年-12月)</t>
+(25年-12月-29日)</t>
         </is>
       </c>
       <c r="C25" s="23" t="inlineStr">
@@ -6938,7 +6938,7 @@
           <t>B | 168呎 (开放式)
 $410万
 $24,429/呎
-(26年-02月)</t>
+(26年-02月-01日)</t>
         </is>
       </c>
       <c r="D25" s="23" t="inlineStr">
@@ -6946,7 +6946,7 @@
           <t>C | 241呎 (开放式)
 $572万
 $23,734/呎
-(26年-02月)</t>
+(26年-02月-24日)</t>
         </is>
       </c>
       <c r="E25" s="23" t="inlineStr">
@@ -6954,7 +6954,7 @@
           <t>D | 244呎 (开放式)
 $557万
 $22,816/呎
-(25年-07月)</t>
+(25年-07月-13日)</t>
         </is>
       </c>
       <c r="F25" s="21" t="inlineStr"/>
@@ -6970,7 +6970,7 @@
           <t>A | 196呎 (开放式)
 $450万
 $22,980/呎
-(25年-03月)</t>
+(25年-03月-30日)</t>
         </is>
       </c>
       <c r="C26" s="23" t="inlineStr">
@@ -6978,7 +6978,7 @@
           <t>B | 168呎 (开放式)
 $406万
 $24,185/呎
-(26年-02月)</t>
+(26年-02月-05日)</t>
         </is>
       </c>
       <c r="D26" s="23" t="inlineStr">
@@ -6986,7 +6986,7 @@
           <t>C | 205呎 (开放式)
 $540万
 $26,322/呎
-(25年-12月)</t>
+(25年-12月-18日)</t>
         </is>
       </c>
       <c r="E26" s="23" t="inlineStr">
@@ -6994,7 +6994,7 @@
           <t>D | 209呎 (开放式)
 $548万
 $26,196/呎
-(24年-11月)</t>
+(24年-11月-18日)</t>
         </is>
       </c>
       <c r="F26" s="21" t="inlineStr"/>
